--- a/data/hero/2026_04/kakao.xlsx
+++ b/data/hero/2026_04/kakao.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="weekly" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="reviews" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weekly" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reviews" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,197 +431,197 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>appearances</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>total_weeks</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_rank</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>best_rank</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>first_rank</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>last_rank</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>first_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>last_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_change</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>first_like</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>last_like</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>like_growth</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>like_growth_pct</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>score_stability</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>score_best_rank</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>score_rank_change</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>score_engagement</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>total_score</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>url</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13255641</v>
+        <v>12610607</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>동아제약</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+5포추가+쇼핑백 증정</t>
+          <t>[단독] 비타그란 비타민C 구미젤리 버라이어티팩 (복숭아/포도/오렌지 3가지맛, 45봉 대용량) + 팝핑스틱 20포 증정</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64900</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
+        <v>28000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://gift.kakao.com/product/12610607</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>293.67</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>393</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="n">
         <v>20260405</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>20260419</v>
       </c>
-      <c r="M2" t="n">
-        <v>109</v>
-      </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>945</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>1328</v>
       </c>
       <c r="Q2" t="n">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="R2" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="S2" t="n">
         <v>30</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>25</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>20</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>76</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>https://gift.kakao.com/product/13255641</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -627,27 +639,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>like</t>
         </is>
@@ -661,13 +673,13 @@
         <v>20260405</v>
       </c>
       <c r="C2" t="n">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="D2" t="n">
-        <v>62000</v>
+        <v>28000</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3">
@@ -678,13 +690,13 @@
         <v>20260412</v>
       </c>
       <c r="C3" t="n">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>62000</v>
+        <v>28000</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="4">
@@ -695,13 +707,13 @@
         <v>20260419</v>
       </c>
       <c r="C4" t="n">
-        <v>284</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>64900</v>
+        <v>28000</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>1328</v>
       </c>
     </row>
   </sheetData>
@@ -719,22 +731,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>review_date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>reviewer</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>content</t>
         </is>
